--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VersioningAttributes/outputfile.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VersioningAttributes/outputfile.xlsx
@@ -1830,9 +1830,9 @@
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pvt2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" outline="1">
   <location ref="A1" firstHeaderRow="0" firstDataRow="0" firstDataCol="0"/>
   <pivotFields count="5">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField name="FullName" axis="axisRow" showAll="0" defaultSubtotal="0">
-      <items count="100">
+    <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
+    <pivotField name="FullName" axis="axisRow" showAll="0">
+      <items count="101">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
@@ -1933,16 +1933,18 @@
         <item x="97"/>
         <item x="98"/>
         <item x="99"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField name="Sex" axis="axisCol" showAll="0" defaultSubtotal="0">
-      <items count="2">
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField name="Sex" axis="axisCol" showAll="0">
+      <items count="3">
         <item x="0"/>
         <item x="1"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="1"/>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VersioningAttributes/outputfile.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VersioningAttributes/outputfile.xlsx
@@ -735,7 +735,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="1" refreshedBy="Francois Botha" refreshedDate="43651.467919212962" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="100">
+<x:pivotCacheDefinition xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="0" refreshedBy="Francois Botha" refreshedDate="43651.467919212962" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="100">
   <x:cacheSource type="worksheet">
     <x:worksheetSource ref="A1:E101" sheet="Data"/>
   </x:cacheSource>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VersioningAttributes/outputfile.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VersioningAttributes/outputfile.xlsx
@@ -1827,7 +1827,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pvt2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" outline="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pvt2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" createdVersion="5" outline="1">
   <location ref="A1" firstHeaderRow="0" firstDataRow="0" firstDataCol="0"/>
   <pivotFields count="5">
     <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VersioningAttributes/outputfile.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VersioningAttributes/outputfile.xlsx
@@ -38,10 +38,19 @@
     <x:t>(All)</x:t>
   </x:si>
   <x:si>
+    <x:t>Row Labels</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Average of Age</x:t>
+  </x:si>
+  <x:si>
     <x:t>Female</x:t>
   </x:si>
   <x:si>
     <x:t>Male</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grand Total</x:t>
   </x:si>
   <x:si>
     <x:t>Id</x:t>
@@ -2245,6 +2254,38 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
+    <x:row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <x:c r="A3" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <x:c r="A4" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>60.8837209302326</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <x:c r="A5" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B5" s="0">
+        <x:v>61.4912280701754</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <x:c r="A6" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B6" s="0">
+        <x:v>61.23</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2271,16 +2312,16 @@
   <x:sheetData>
     <x:row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <x:c r="A1" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
         <x:v>0</x:v>
@@ -2291,16 +2332,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>99</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2308,16 +2349,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C3" s="0">
         <x:v>58</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2325,16 +2366,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2342,16 +2383,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0">
         <x:v>98</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2359,16 +2400,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>64</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2376,16 +2417,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>33</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2393,16 +2434,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C8" s="0">
         <x:v>31</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2410,16 +2451,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C9" s="0">
         <x:v>64</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2427,16 +2468,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C10" s="0">
         <x:v>46</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2444,16 +2485,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C11" s="0">
         <x:v>63</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2461,16 +2502,16 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>95</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2478,16 +2519,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C13" s="0">
         <x:v>90</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2495,16 +2536,16 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C14" s="0">
         <x:v>51</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2512,16 +2553,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C15" s="0">
         <x:v>82</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2529,16 +2570,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C16" s="0">
         <x:v>88</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -2546,16 +2587,16 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C17" s="0">
         <x:v>34</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -2563,16 +2604,16 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>79</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2580,16 +2621,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>84</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2597,16 +2638,16 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>51</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -2614,16 +2655,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C21" s="0">
         <x:v>40</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -2631,16 +2672,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C22" s="0">
         <x:v>48</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -2648,16 +2689,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C23" s="0">
         <x:v>49</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -2665,16 +2706,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C24" s="0">
         <x:v>82</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -2682,16 +2723,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C25" s="0">
         <x:v>83</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -2699,16 +2740,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C26" s="0">
         <x:v>71</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -2716,16 +2757,16 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C27" s="0">
         <x:v>91</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -2733,16 +2774,16 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C28" s="0">
         <x:v>88</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2750,16 +2791,16 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C29" s="0">
         <x:v>81</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -2767,16 +2808,16 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C30" s="0">
         <x:v>87</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -2784,16 +2825,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C31" s="0">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -2801,16 +2842,16 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C32" s="0">
         <x:v>45</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2818,16 +2859,16 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C33" s="0">
         <x:v>66</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2835,16 +2876,16 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C34" s="0">
         <x:v>67</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -2852,16 +2893,16 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C35" s="0">
         <x:v>94</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2869,16 +2910,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C36" s="0">
         <x:v>43</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2886,16 +2927,16 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C37" s="0">
         <x:v>71</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2903,16 +2944,16 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C38" s="0">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2920,16 +2961,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C39" s="0">
         <x:v>99</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -2937,16 +2978,16 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C40" s="0">
         <x:v>64</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2954,16 +2995,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C41" s="0">
         <x:v>60</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2971,16 +3012,16 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C42" s="0">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2988,16 +3029,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C43" s="0">
         <x:v>46</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3005,16 +3046,16 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C44" s="0">
         <x:v>81</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -3022,16 +3063,16 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C45" s="0">
         <x:v>80</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -3039,16 +3080,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C46" s="0">
         <x:v>51</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -3056,16 +3097,16 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C47" s="0">
         <x:v>65</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3073,16 +3114,16 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C48" s="0">
         <x:v>36</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3090,16 +3131,16 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C49" s="0">
         <x:v>31</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -3107,16 +3148,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C50" s="0">
         <x:v>58</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -3124,16 +3165,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C51" s="0">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -3141,16 +3182,16 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C52" s="0">
         <x:v>75</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -3158,16 +3199,16 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C53" s="0">
         <x:v>45</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -3175,16 +3216,16 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C54" s="0">
         <x:v>43</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -3192,16 +3233,16 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C55" s="0">
         <x:v>44</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -3209,16 +3250,16 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C56" s="0">
         <x:v>52</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3226,16 +3267,16 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C57" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -3243,16 +3284,16 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C58" s="0">
         <x:v>59</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -3260,16 +3301,16 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C59" s="0">
         <x:v>40</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -3277,16 +3318,16 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C60" s="0">
         <x:v>53</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -3294,16 +3335,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C61" s="0">
         <x:v>31</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3311,16 +3352,16 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C62" s="0">
         <x:v>63</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -3328,16 +3369,16 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C63" s="0">
         <x:v>34</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -3345,16 +3386,16 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C64" s="0">
         <x:v>65</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -3362,16 +3403,16 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C65" s="0">
         <x:v>67</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -3379,16 +3420,16 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C66" s="0">
         <x:v>35</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -3396,16 +3437,16 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C67" s="0">
         <x:v>81</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -3413,16 +3454,16 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C68" s="0">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -3430,16 +3471,16 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C69" s="0">
         <x:v>92</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -3447,16 +3488,16 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C70" s="0">
         <x:v>37</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3464,16 +3505,16 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C71" s="0">
         <x:v>43</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3481,16 +3522,16 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C72" s="0">
         <x:v>41</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3498,16 +3539,16 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C73" s="0">
         <x:v>45</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3515,16 +3556,16 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C74" s="0">
         <x:v>92</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3532,16 +3573,16 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C75" s="0">
         <x:v>24</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -3549,16 +3590,16 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C76" s="0">
         <x:v>44</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -3566,16 +3607,16 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C77" s="0">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -3583,16 +3624,16 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C78" s="0">
         <x:v>96</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -3600,16 +3641,16 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C79" s="0">
         <x:v>71</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>166</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -3617,16 +3658,16 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C80" s="0">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -3634,16 +3675,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C81" s="0">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -3651,16 +3692,16 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C82" s="0">
         <x:v>67</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -3668,16 +3709,16 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C83" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -3685,16 +3726,16 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C84" s="0">
         <x:v>43</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -3702,16 +3743,16 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C85" s="0">
         <x:v>90</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -3719,16 +3760,16 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C86" s="0">
         <x:v>49</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -3736,16 +3777,16 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C87" s="0">
         <x:v>47</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -3753,16 +3794,16 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C88" s="0">
         <x:v>82</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -3770,16 +3811,16 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C89" s="0">
         <x:v>95</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -3787,16 +3828,16 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C90" s="0">
         <x:v>47</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -3804,16 +3845,16 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C91" s="0">
         <x:v>47</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -3821,16 +3862,16 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C92" s="0">
         <x:v>70</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -3838,16 +3879,16 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C93" s="0">
         <x:v>81</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -3855,16 +3896,16 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C94" s="0">
         <x:v>94</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -3872,16 +3913,16 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C95" s="0">
         <x:v>57</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -3889,16 +3930,16 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C96" s="0">
         <x:v>82</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -3906,16 +3947,16 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C97" s="0">
         <x:v>33</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -3923,16 +3964,16 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C98" s="0">
         <x:v>99</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -3940,16 +3981,16 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C99" s="0">
         <x:v>54</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -3957,16 +3998,16 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C100" s="0">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -3974,16 +4015,16 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C101" s="0">
         <x:v>46</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VersioningAttributes/outputfile.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VersioningAttributes/outputfile.xlsx
@@ -1826,7 +1826,7 @@
   <dataFields count="1">
     <dataField name="Average of Age" fld="2" subtotal="average" baseField="3" baseItem="0"/>
   </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1"/>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition enableEdit="0" hideValuesRow="1"/>
